--- a/data/trans_orig/P04C04_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04C04_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con refrigeración por aire acondicionado mediante aparatos móviles (NO ventiladores) en la vivienda en 2023</t>
+          <t>Población según si dispone de refrigeración por aire acondicionado mediante aparatos móviles (NO ventiladores) en la vivienda en 2023 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>280551</t>
+          <t>279528</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>299844</t>
+          <t>299218</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>276277</t>
+          <t>276166</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>284482</t>
+          <t>284671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>560791</t>
+          <t>562083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>582511</t>
+          <t>582846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>846</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30091</t>
+          <t>31909</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18046</t>
+          <t>17183</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39534</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>444452</t>
+          <t>442061</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>482643</t>
+          <t>481041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>457052</t>
+          <t>457007</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480557</t>
+          <t>480711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>912926</t>
+          <t>911905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>956739</t>
+          <t>954488</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33494</t>
+          <t>34912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70840</t>
+          <t>74305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33259</t>
+          <t>32966</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57117</t>
+          <t>56175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72924</t>
+          <t>74986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116956</t>
+          <t>116076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>287923</t>
+          <t>287904</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>302559</t>
+          <t>302991</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>314756</t>
+          <t>314389</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>329973</t>
+          <t>330877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>609465</t>
+          <t>606640</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>630090</t>
+          <t>628992</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -1755,97 +1755,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1686</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1248</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1425</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24774</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33729</t>
+          <t>34096</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>32190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51717</t>
+          <t>54542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>237808</t>
+          <t>237010</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>278758</t>
+          <t>280218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>216103</t>
+          <t>213000</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>408610</t>
+          <t>408006</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>439734</t>
+          <t>450247</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>675251</t>
+          <t>676511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31072</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71838</t>
+          <t>72919</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62614</t>
+          <t>62611</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257452</t>
+          <t>260566</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>104785</t>
+          <t>103878</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>345379</t>
+          <t>332833</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75707</t>
+          <t>74139</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>98673</t>
+          <t>97981</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47027</t>
+          <t>45851</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109116</t>
+          <t>109754</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112303</t>
+          <t>113448</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>198815</t>
+          <t>200213</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77890</t>
+          <t>78347</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101346</t>
+          <t>102639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146119</t>
+          <t>144846</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>209945</t>
+          <t>211375</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>232396</t>
+          <t>230867</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>321915</t>
+          <t>319152</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,01%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>242017</t>
+          <t>241851</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>258504</t>
+          <t>258273</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>231837</t>
+          <t>232562</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>245288</t>
+          <t>245859</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>480167</t>
+          <t>480336</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>501029</t>
+          <t>500157</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24886</t>
+          <t>24250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>22567</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>22499</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41803</t>
+          <t>41514</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>390568</t>
+          <t>388945</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>449670</t>
+          <t>447432</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>634463</t>
+          <t>631897</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>767402</t>
+          <t>781794</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1042038</t>
+          <t>1042451</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1251858</t>
+          <t>1252145</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,4%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>17187</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44106</t>
+          <t>43343</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37147</t>
+          <t>36607</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28928</t>
+          <t>29835</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69369</t>
+          <t>71877</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>146628</t>
+          <t>148204</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>205571</t>
+          <t>208071</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67037</t>
+          <t>50901</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>179740</t>
+          <t>180282</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>182236</t>
+          <t>186092</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>365571</t>
+          <t>367538</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>283465</t>
+          <t>301354</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>872827</t>
+          <t>873446</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>642597</t>
+          <t>643152</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>667006</t>
+          <t>668308</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>765034</t>
+          <t>761026</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1526885</t>
+          <t>1528765</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>48456</t>
+          <t>47184</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>643002</t>
+          <t>622546</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>42187</t>
+          <t>42227</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>65667</t>
+          <t>66577</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>104256</t>
+          <t>101777</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>883844</t>
+          <t>870178</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2102193</t>
+          <t>2147876</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2942420</t>
+          <t>2941233</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2889787</t>
+          <t>2872427</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3208364</t>
+          <t>3200684</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5102985</t>
+          <t>5088981</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6071938</t>
+          <t>6071245</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>30148</t>
+          <t>28163</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>62967</t>
+          <t>60444</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>50769</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,47 +4541,47 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>79903</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>61555</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>101236</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
           <t>1,41%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>79903</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>60537</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>100332</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>463856</t>
+          <t>466962</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1317017</t>
+          <t>1275292</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>461788</t>
+          <t>461635</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>784780</t>
+          <t>791573</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>998771</t>
+          <t>1000538</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1989538</t>
+          <t>2000420</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04C04_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04C04_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>292367</t>
+          <t>301964</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>279528</t>
+          <t>293044</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>299218</t>
+          <t>308362</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>281271</t>
+          <t>306661</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>276166</t>
+          <t>300455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>284671</t>
+          <t>310353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>573637</t>
+          <t>608624</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>562083</t>
+          <t>598565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>582846</t>
+          <t>617028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>836</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>872</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18094</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11397</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31909</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13284</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>26291</t>
+          <t>24574</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>34465</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>465962</t>
+          <t>475331</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>442061</t>
+          <t>455618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481041</t>
+          <t>491864</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>470305</t>
+          <t>496859</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>457007</t>
+          <t>481339</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480711</t>
+          <t>509492</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>936267</t>
+          <t>972190</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911905</t>
+          <t>949126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954488</t>
+          <t>992887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>592</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>49689</t>
+          <t>52596</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34912</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74305</t>
+          <t>72477</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>43555</t>
+          <t>48475</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>35845</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56175</t>
+          <t>63796</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>93244</t>
+          <t>101071</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74986</t>
+          <t>81108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116076</t>
+          <t>124869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>517077</t>
+          <t>529314</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517077</t>
+          <t>529314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517077</t>
+          <t>529314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514442</t>
+          <t>545926</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514442</t>
+          <t>545926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514442</t>
+          <t>545926</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1031519</t>
+          <t>1075239</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1031519</t>
+          <t>1075239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1031519</t>
+          <t>1075239</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,102 +1637,102 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>297060</t>
+          <t>295754</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>287904</t>
+          <t>287109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>302991</t>
+          <t>301404</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>92,29%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>96,89%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>329297</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>320568</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>336205</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>92,57%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>90,11%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>94,51%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>625051</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>613963</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>635487</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>93,73%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>92,07%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>96,9%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>322911</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>314389</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>330877</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>90,22%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>619971</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>606640</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>628992</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>93,77%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -1863,102 +1863,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15637</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>26448</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19540</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>35177</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>41779</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>31343</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>52867</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>7,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>25574</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>17608</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>34096</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>41211</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>32190</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>54542</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312697</t>
+          <t>311085</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312697</t>
+          <t>311085</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312697</t>
+          <t>311085</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>348485</t>
+          <t>355745</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>348485</t>
+          <t>355745</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>348485</t>
+          <t>355745</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>661182</t>
+          <t>666830</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>661182</t>
+          <t>666830</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>661182</t>
+          <t>666830</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>264064</t>
+          <t>321732</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>237010</t>
+          <t>299885</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>280218</t>
+          <t>337385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>343138</t>
+          <t>351974</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>213000</t>
+          <t>335403</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>408006</t>
+          <t>364941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>607201</t>
+          <t>673706</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>450247</t>
+          <t>649064</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>676511</t>
+          <t>696552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,22 +2276,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>13441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45210</t>
+          <t>47942</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29800</t>
+          <t>32707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72919</t>
+          <t>69844</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>128301</t>
+          <t>64700</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62611</t>
+          <t>52040</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>260566</t>
+          <t>80490</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>173511</t>
+          <t>112641</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>103878</t>
+          <t>90957</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>332833</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>474944</t>
+          <t>420308</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>474944</t>
+          <t>420308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>474944</t>
+          <t>420308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>787500</t>
+          <t>793453</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>787500</t>
+          <t>793453</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>787500</t>
+          <t>793453</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>86729</t>
+          <t>100670</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74139</t>
+          <t>89351</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97981</t>
+          <t>114129</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>85148</t>
+          <t>93911</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45851</t>
+          <t>83294</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109754</t>
+          <t>105942</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>171876</t>
+          <t>194581</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113448</t>
+          <t>179021</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>200213</t>
+          <t>212436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>10334</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>89942</t>
+          <t>100729</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78347</t>
+          <t>87532</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>102639</t>
+          <t>112973</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>170201</t>
+          <t>131140</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>144846</t>
+          <t>119040</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>211375</t>
+          <t>141821</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>260143</t>
+          <t>231869</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230867</t>
+          <t>214003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>319152</t>
+          <t>247164</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>258403</t>
+          <t>228512</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>258403</t>
+          <t>228512</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258403</t>
+          <t>228512</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>437144</t>
+          <t>434177</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>437144</t>
+          <t>434177</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>437144</t>
+          <t>434177</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>252031</t>
+          <t>252808</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>241851</t>
+          <t>243912</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>258273</t>
+          <t>259407</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>240031</t>
+          <t>246220</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>232562</t>
+          <t>238252</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>245859</t>
+          <t>251538</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>492061</t>
+          <t>499028</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>480336</t>
+          <t>486816</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>500157</t>
+          <t>507766</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>806</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15165</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24250</t>
+          <t>23715</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,27 +3266,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>16111</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22567</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>30785</t>
+          <t>30987</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22499</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41514</t>
+          <t>41425</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>420675</t>
+          <t>498579</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>388945</t>
+          <t>468135</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>447432</t>
+          <t>527065</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>691001</t>
+          <t>585959</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>631897</t>
+          <t>562707</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>781794</t>
+          <t>608303</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1111677</t>
+          <t>1084537</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1042451</t>
+          <t>1038788</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1252145</t>
+          <t>1119437</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>27123</t>
+          <t>29426</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>43343</t>
+          <t>45994</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>22378</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36607</t>
+          <t>37697</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>49501</t>
+          <t>53844</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29835</t>
+          <t>40410</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71877</t>
+          <t>73497</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>174565</t>
+          <t>188732</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>148204</t>
+          <t>163517</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>208071</t>
+          <t>217280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>130464</t>
+          <t>156093</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>50901</t>
+          <t>136184</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>180282</t>
+          <t>177448</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>305029</t>
+          <t>344825</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>186092</t>
+          <t>308172</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>367538</t>
+          <t>386686</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>622363</t>
+          <t>716737</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>622363</t>
+          <t>716737</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>622363</t>
+          <t>716737</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>843843</t>
+          <t>766470</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>843843</t>
+          <t>766470</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>843843</t>
+          <t>766470</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1466207</t>
+          <t>1483207</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1466207</t>
+          <t>1483207</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1466207</t>
+          <t>1483207</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>638544</t>
+          <t>745212</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>301354</t>
+          <t>727101</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>873446</t>
+          <t>758397</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>655372</t>
+          <t>758646</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>643152</t>
+          <t>743585</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>668308</t>
+          <t>771949</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1293917</t>
+          <t>1503858</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>761026</t>
+          <t>1481337</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1528765</t>
+          <t>1521598</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>20178</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>284228</t>
+          <t>46289</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>47184</t>
+          <t>33424</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>622546</t>
+          <t>64166</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>53617</t>
+          <t>62438</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>42227</t>
+          <t>50116</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>66577</t>
+          <t>78079</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>337844</t>
+          <t>108727</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>101777</t>
+          <t>91179</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>870178</t>
+          <t>131738</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>927754</t>
+          <t>797025</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>927754</t>
+          <t>797025</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>927754</t>
+          <t>797025</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>715492</t>
+          <t>828780</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>715492</t>
+          <t>828780</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>715492</t>
+          <t>828780</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1643246</t>
+          <t>1625805</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1643246</t>
+          <t>1625805</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1643246</t>
+          <t>1625805</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2717431</t>
+          <t>2992049</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2147876</t>
+          <t>2941745</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2941233</t>
+          <t>3041609</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3089176</t>
+          <t>3169527</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2872427</t>
+          <t>3128514</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3200684</t>
+          <t>3202815</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>5806606</t>
+          <t>6161577</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5088981</t>
+          <t>6098313</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6071245</t>
+          <t>6219832</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>42307</t>
+          <t>47934</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>34198</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>60444</t>
+          <t>67060</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>37596</t>
+          <t>42091</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>50769</t>
+          <t>57729</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>79903</t>
+          <t>90024</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>61555</t>
+          <t>72820</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>101236</t>
+          <t>114303</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>692530</t>
+          <t>482539</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>466962</t>
+          <t>436883</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1275292</t>
+          <t>532983</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>575527</t>
+          <t>513934</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>461635</t>
+          <t>480572</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>791573</t>
+          <t>552839</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1268057</t>
+          <t>996473</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1000538</t>
+          <t>936725</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2000420</t>
+          <t>1062275</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3452268</t>
+          <t>3522522</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3452268</t>
+          <t>3522522</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3452268</t>
+          <t>3522522</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3702299</t>
+          <t>3725552</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3702299</t>
+          <t>3725552</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3702299</t>
+          <t>3725552</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7154566</t>
+          <t>7248074</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7154566</t>
+          <t>7248074</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7154566</t>
+          <t>7248074</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
